--- a/xls/square_16_quad4_23.xlsx
+++ b/xls/square_16_quad4_23.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21">
+        <v>576</v>
+      </c>
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21">
+        <v>289</v>
+      </c>
+      <c r="E21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21">
+        <v>484</v>
+      </c>
+      <c r="G21" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21">
+        <v>1323</v>
+      </c>
+      <c r="I21">
+        <v>-0.35878535434728526</v>
+      </c>
+      <c r="J21">
+        <v>-1.3562680073499371</v>
+      </c>
+      <c r="K21">
+        <v>2.420539612376298</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22">
+        <v>576</v>
+      </c>
+      <c r="C22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22">
+        <v>289</v>
+      </c>
+      <c r="E22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22">
+        <v>529</v>
+      </c>
+      <c r="G22" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22">
+        <v>1452</v>
+      </c>
+      <c r="I22">
+        <v>-1.1909250922794437</v>
+      </c>
+      <c r="J22">
+        <v>-1.3368168092676276</v>
+      </c>
+      <c r="K22">
+        <v>1.8895932354635794</v>
+      </c>
+    </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
         <v>11</v>
@@ -482,13 +552,13 @@
         <v>1587</v>
       </c>
       <c r="I23">
-        <v>-1.5402477351818868</v>
+        <v>-1.1152618346707601</v>
       </c>
       <c r="J23">
-        <v>-1.5892647691980868</v>
+        <v>-1.1778617869077708</v>
       </c>
       <c r="K23">
-        <v>1.9040338722640882</v>
+        <v>4.299099976995965</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -517,13 +587,13 @@
         <v>1728</v>
       </c>
       <c r="I24">
-        <v>-1.5286633474362001</v>
+        <v>-1.094058612861059</v>
       </c>
       <c r="J24">
-        <v>-1.4754048988909347</v>
+        <v>-0.9998284398966149</v>
       </c>
       <c r="K24">
-        <v>2.55263726284804</v>
+        <v>4.663779608802064</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -552,13 +622,13 @@
         <v>1875</v>
       </c>
       <c r="I25">
-        <v>-1.4264058766069583</v>
+        <v>-0.2295275622990854</v>
       </c>
       <c r="J25">
-        <v>-1.0488307764050004</v>
+        <v>-0.2062813730352666</v>
       </c>
       <c r="K25">
-        <v>2.9183324736713323</v>
+        <v>4.874970399400637</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -587,13 +657,13 @@
         <v>2028</v>
       </c>
       <c r="I26">
-        <v>-0.4279105240798395</v>
+        <v>-0.0033272897186327334</v>
       </c>
       <c r="J26">
-        <v>-0.3123803143527046</v>
+        <v>-0.0028451444413231707</v>
       </c>
       <c r="K26">
-        <v>3.837833433277971</v>
+        <v>4.101805948905634</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -622,13 +692,13 @@
         <v>2187</v>
       </c>
       <c r="I27">
-        <v>-0.003946643409595663</v>
+        <v>-3.0154015395882458e-5</v>
       </c>
       <c r="J27">
-        <v>-0.003919989143767094</v>
+        <v>-3.171311406005933e-5</v>
       </c>
       <c r="K27">
-        <v>3.2298405974120232</v>
+        <v>3.2399361777512263</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -657,13 +727,13 @@
         <v>2352</v>
       </c>
       <c r="I28">
-        <v>-0.004610745780116436</v>
+        <v>-3.3323632634137174e-5</v>
       </c>
       <c r="J28">
-        <v>-0.0047142064632359655</v>
+        <v>-3.476807149995032e-5</v>
       </c>
       <c r="K28">
-        <v>3.279387355462154</v>
+        <v>3.2323649256124916</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -692,13 +762,13 @@
         <v>2523</v>
       </c>
       <c r="I29">
-        <v>-0.0030953472612146363</v>
+        <v>-2.2914039129603133e-5</v>
       </c>
       <c r="J29">
-        <v>-0.0033465881196333078</v>
+        <v>-2.4990214580441333e-5</v>
       </c>
       <c r="K29">
-        <v>3.230508203949865</v>
+        <v>3.163305309017808</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -727,13 +797,13 @@
         <v>2700</v>
       </c>
       <c r="I30">
-        <v>-0.0009185285221017516</v>
+        <v>-7.362531149988811e-6</v>
       </c>
       <c r="J30">
-        <v>-0.0009973698167183936</v>
+        <v>-7.993145123828715e-6</v>
       </c>
       <c r="K30">
-        <v>2.993452736336296</v>
+        <v>2.9141908414344306</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -762,13 +832,13 @@
         <v>2883</v>
       </c>
       <c r="I31">
-        <v>-0.002356593106632166</v>
+        <v>-1.548961028510181e-5</v>
       </c>
       <c r="J31">
-        <v>-0.002701259320481497</v>
+        <v>-1.769682136532945e-5</v>
       </c>
       <c r="K31">
-        <v>3.1971684851657334</v>
+        <v>3.0917602797233257</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -797,13 +867,13 @@
         <v>3072</v>
       </c>
       <c r="I32">
-        <v>-0.0004883426100678423</v>
+        <v>-3.1973163721706403e-6</v>
       </c>
       <c r="J32">
-        <v>-0.0005585526091927277</v>
+        <v>-3.7531501572788503e-6</v>
       </c>
       <c r="K32">
-        <v>2.8804908495262223</v>
+        <v>2.763190743316527</v>
       </c>
     </row>
   </sheetData>
